--- a/artfynd/A 3952-2025 artfynd.xlsx
+++ b/artfynd/A 3952-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56124214</v>
+        <v>56123582</v>
       </c>
       <c r="B2" t="n">
-        <v>96319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>102021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633722.1270960377</v>
+        <v>633835</v>
       </c>
       <c r="R2" t="n">
-        <v>6719197.842455321</v>
+        <v>6719186</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,69 +791,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56123582</v>
+        <v>56090178</v>
       </c>
       <c r="B3" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102021</v>
+        <v>201164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västanå, Ä-by golfbana, Upl</t>
+          <t>Golfbanan, Västanå, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633834.890643746</v>
+        <v>633822</v>
       </c>
       <c r="R3" t="n">
-        <v>6719185.801885958</v>
+        <v>6719266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,22 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tommy Löfgren, Pär Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113280112</v>
+        <v>56092137</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,34 +903,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Golfbanan, Västanå, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633726</v>
+        <v>633681</v>
       </c>
       <c r="R4" t="n">
-        <v>6719181</v>
+        <v>6719249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,31 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113280111</v>
+        <v>113280112</v>
       </c>
       <c r="B5" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633725</v>
+        <v>633726</v>
       </c>
       <c r="R5" t="n">
-        <v>6719178</v>
+        <v>6719181</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113280124</v>
+        <v>113280113</v>
       </c>
       <c r="B6" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633685</v>
+        <v>633721</v>
       </c>
       <c r="R6" t="n">
-        <v>6719232</v>
+        <v>6719179</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113280114</v>
+        <v>113280115</v>
       </c>
       <c r="B7" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633721</v>
+        <v>633720</v>
       </c>
       <c r="R7" t="n">
-        <v>6719177</v>
+        <v>6719176</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113280122</v>
+        <v>113280116</v>
       </c>
       <c r="B8" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633698</v>
+        <v>633716</v>
       </c>
       <c r="R8" t="n">
-        <v>6719209</v>
+        <v>6719171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,15 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113280119</v>
+        <v>56090929</v>
       </c>
       <c r="B9" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,34 +1413,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219799</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Golfbanan, Västanå, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633715</v>
+        <v>633669</v>
       </c>
       <c r="R9" t="n">
-        <v>6719198</v>
+        <v>6719237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,12 +1476,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2015-07-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,31 +1496,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113280113</v>
+        <v>56124214</v>
       </c>
       <c r="B10" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,16 +1519,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>219799</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1596,17 +1536,26 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hundskogen, Upl</t>
+          <t>Västanå, Ä-by golfbana, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633721</v>
+        <v>633722</v>
       </c>
       <c r="R10" t="n">
-        <v>6719179</v>
+        <v>6719198</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,12 +1582,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,31 +1602,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Brodin</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rätz</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113280120</v>
+        <v>113280192</v>
       </c>
       <c r="B11" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>219799</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633694</v>
+        <v>633711</v>
       </c>
       <c r="R11" t="n">
-        <v>6719197</v>
+        <v>6719214</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113280192</v>
+        <v>113280193</v>
       </c>
       <c r="B12" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633711</v>
+        <v>633722</v>
       </c>
       <c r="R12" t="n">
-        <v>6719214</v>
+        <v>6719191</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,15 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113280116</v>
+        <v>113280111</v>
       </c>
       <c r="B13" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633716</v>
+        <v>633725</v>
       </c>
       <c r="R13" t="n">
-        <v>6719171</v>
+        <v>6719178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,15 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113280193</v>
+        <v>113280114</v>
       </c>
       <c r="B14" t="n">
-        <v>97635</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219799</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633722</v>
+        <v>633721</v>
       </c>
       <c r="R14" t="n">
-        <v>6719191</v>
+        <v>6719177</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,15 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113280118</v>
+        <v>113280117</v>
       </c>
       <c r="B15" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633723</v>
+        <v>633710</v>
       </c>
       <c r="R15" t="n">
-        <v>6719195</v>
+        <v>6719189</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,15 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113280115</v>
+        <v>113280118</v>
       </c>
       <c r="B16" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,21 +2130,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2239,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633720</v>
+        <v>633723</v>
       </c>
       <c r="R16" t="n">
-        <v>6719176</v>
+        <v>6719195</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2305,15 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113280117</v>
+        <v>113280119</v>
       </c>
       <c r="B17" t="n">
-        <v>97673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633710</v>
+        <v>633715</v>
       </c>
       <c r="R17" t="n">
-        <v>6719189</v>
+        <v>6719198</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,6 +2318,613 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113280120</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>633694</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6719197</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113280122</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>633698</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6719209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113280123</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>633700</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6719244</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113280124</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>633685</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6719232</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113280125</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hundskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>633680</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6719235</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88767667</v>
+      </c>
+      <c r="B23" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>633611</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6719235</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-05-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3952-2025 artfynd.xlsx
+++ b/artfynd/A 3952-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56123582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56092137</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280113</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124214</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280193</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280111</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280114</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280117</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280118</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280119</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280120</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280123</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280124</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
           <t>ASC0007 Gästrike vatten Hundskogen NVI</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113280125</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,8 +3035,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88767667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>